--- a/assessment_forms/015_self_assessment_tool_form--assessment_forms.xlsx
+++ b/assessment_forms/015_self_assessment_tool_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How do you rate your self-awareness</t>
+          <t>What are your top 3 core values that guide your decision-making?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What are your strengths</t>
+          <t>How would you rate your ability to set and achieve goals?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What are your weaknesses</t>
+          <t>What are your top 3 priorities for the next 6 months?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What are your values</t>
+          <t>How do you rate your level of self-awareness regarding your strengths and weaknesses?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What are your skills</t>
+          <t>What are your top 3 skills that you are confident in?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What are your abilities</t>
+          <t>How do you rate your motivation to pursue personal and professional development?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How do you rate your self-esteem</t>
+          <t>What are your top 3 areas of interest?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What are your skills</t>
+          <t>How do you rate your confidence in your skills and abilities?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How do you rate your self-awareness</t>
+          <t>What are your top 3 values that drive your decisions?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What are your values</t>
+          <t>How do you rate your ability to set and achieve long-term goals?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What are your abilities</t>
+          <t>What are your top 3 skills that you want to develop further?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How do you rate your skills</t>
+          <t>How do you rate your level of self-acceptance and self-compassion?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What are your goals</t>
+          <t>What are your top 3 goals for career development and advancement?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How do you rate your goals</t>
+          <t>How do you rate your ability to overcome obstacles and challenges?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What are your motivations</t>
+          <t>What are your top 3 priorities for your personal and professional life?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How do you rate your motivations</t>
+          <t>How do you rate your level of self-motivation and drive?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What are your priorities</t>
+          <t>What are your top 3 goals for personal growth and development?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How do you rate your priorities</t>
+          <t>How do you rate your ability to stay motivated and focused?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What are your interests</t>
+          <t>What are your top 3 values that you live by?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,126 +962,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How do you rate your interests</t>
+          <t>How do you rate your ability to adapt to change?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What are your values</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How do you rate your values</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What are your skills</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How do you rate your skills</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What are your goals</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'strong'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Strong'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'average'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Average'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1165,777 +1050,522 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'weak'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Weak'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_2_choices</t>
+          <t>self_assessment_tool_form_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_2_choices</t>
+          <t>self_assessment_tool_form_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_2_choices</t>
+          <t>self_assessment_tool_form_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_3_choices</t>
+          <t>self_assessment_tool_form_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_3_choices</t>
+          <t>self_assessment_tool_form_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_3_choices</t>
+          <t>self_assessment_tool_form_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_4_choices</t>
+          <t>self_assessment_tool_form_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_4_choices</t>
+          <t>self_assessment_tool_form_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_4_choices</t>
+          <t>self_assessment_tool_form_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_5_choices</t>
+          <t>self_assessment_tool_form_7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_5_choices</t>
+          <t>self_assessment_tool_form_7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_5_choices</t>
+          <t>self_assessment_tool_form_7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_6_choices</t>
+          <t>self_assessment_tool_form_9_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_6_choices</t>
+          <t>self_assessment_tool_form_9_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_6_choices</t>
+          <t>self_assessment_tool_form_9_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_8_choices</t>
+          <t>self_assessment_tool_form_11_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_8_choices</t>
+          <t>self_assessment_tool_form_11_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_8_choices</t>
+          <t>self_assessment_tool_form_11_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_10_choices</t>
+          <t>self_assessment_tool_form_13_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_10_choices</t>
+          <t>self_assessment_tool_form_13_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_10_choices</t>
+          <t>self_assessment_tool_form_13_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_11_choices</t>
+          <t>self_assessment_tool_form_15_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_11_choices</t>
+          <t>self_assessment_tool_form_15_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_11_choices</t>
+          <t>self_assessment_tool_form_15_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_13_choices</t>
+          <t>self_assessment_tool_form_17_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_13_choices</t>
+          <t>self_assessment_tool_form_17_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_13_choices</t>
+          <t>self_assessment_tool_form_17_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_15_choices</t>
+          <t>self_assessment_tool_form_19_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_15_choices</t>
+          <t>self_assessment_tool_form_19_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>self_assessment_tool_form_15_choices</t>
+          <t>self_assessment_tool_form_19_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_17_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'high'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'High'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_17_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_17_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'low'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'high'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'High'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_19_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'low'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'high'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'High'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_21_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'low'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_23_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'high'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'High'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_23_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_23_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'low'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_25_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'high'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'High'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_25_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>self_assessment_tool_form_25_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'low'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
